--- a/stories/arbres/ATOM-REL.CON.001-07.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hadrien joue au parc. Le sable est tiède. Un camarade le bouscule près du bac. Hadrien sent son épaule. Il dit : stop. Il recule. Il peut s'éloigner. Il s'éloigne vers le banc. Papa est le parent au parc. Hadrien va vers papa. Il dit : j'ai dit stop. Papa l'écoute. Hadrien souffle. Plus tard, près des balançoires, un camarade le bouscule encore. Même leçon, autre jeu. Hadrien dit : stop. Il peut s'éloigner. Il rejoint le parent au parc. Papa est sur le banc. Hadrien prend sa main. Papa dit : tu as bien fait. On dit stop. On s'éloigne. On va vers papa ou maman, le parent au parc.</t>
+          <t>Hadrien joue au parc. Le sable est tiède. Un camarade le bouscule près du bac. Hadrien sent son épaule. Stop. Il recule. Il peut s'éloigner. Il s'éloigne vers le banc. Papa est le parent au parc. Hadrien va vers papa. J'ai dit stop. Papa l'écoute. Hadrien souffle. Plus tard, près des balançoires, un camarade le bouscule encore. Même leçon, autre jeu. Stop. Il peut s'éloigner. Il rejoint le parent au parc. Papa est sur le banc. Hadrien prend sa main. Tu as bien fait. On dit stop. On s'éloigne. On va vers papa ou maman, le parent au parc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hadrien joue au parc. Le sable est tiède. Un camarade le bouscule près du bac. Hadrien sent son épaule.
+narrateur|Stop. Il recule. Il peut s'éloigner.
+narrateur|Il s'éloigne vers le banc. Papa est le parent au parc. Hadrien va vers papa.
+narrateur|J'ai dit stop. Papa l'écoute.
+narrateur|Hadrien souffle. Plus tard, près des balançoires, un camarade le bouscule encore. Même leçon, autre jeu.
+enfant-m|Stop. Il peut s'éloigner. Il rejoint le parent au parc. Papa est sur le banc.
+narrateur|Hadrien prend sa main.
+papa|Tu as bien fait. On dit stop. On s'éloigne. On va vers papa ou maman, le parent au parc.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Un camarade bouscule Hadrien. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hadrien a dit stop. Au bac, puis aux balançoires. Il a pu s'éloigner. Il a rejoint le parent au parc.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hadrien reste près du banc. Papa lui tient la main.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.001-07.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,11 @@
 papa|Tu as bien fait. On dit stop. On s'éloigne. On va vers papa ou maman, le parent au parc.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1510,7 @@
           <t>narrateur|Un camarade bouscule Hadrien. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1682,11 @@
           <t>narrateur|Hadrien a dit stop. Au bac, puis aux balançoires. Il a pu s'éloigner. Il a rejoint le parent au parc.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1854,7 @@
           <t>narrateur|Hadrien reste près du banc. Papa lui tient la main.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2065,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2280,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.001-07.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hadrien dit stop au parc</t>
+          <t>Les chaînes des balançoires de Nino</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les chaînes tintent. Nino joue au bac, puis aux balançoires. Deux fois, il dit stop, s'éloigne, rejoint papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hadrien joue au parc. Le sable est tiède. Un camarade le bouscule près du bac. Hadrien sent son épaule. Stop. Il recule. Il peut s'éloigner. Il s'éloigne vers le banc. Papa est le parent au parc. Hadrien va vers papa. J'ai dit stop. Papa l'écoute. Hadrien souffle. Plus tard, près des balançoires, un camarade le bouscule encore. Même leçon, autre jeu. Stop. Il peut s'éloigner. Il rejoint le parent au parc. Papa est sur le banc. Hadrien prend sa main. Tu as bien fait. On dit stop. On s'éloigne. On va vers papa ou maman, le parent au parc.</t>
+          <t>Les chaînes des balançoires font un petit tintement. Un nuage ressemble à un mouton, tout lent. Une feuille sèche est posée sur un siège. Le sable du bac est tiède, presque doux. Papa étale sa veste sur le banc. La veste sent le savon et le vent. Nino, tu entends les chaînes ? Oui. Ça tinte, papa. Le bac est tiède. Les balançoires aussi, plus tard. En ce moment, Nino creuse au bac. Le sable coule entre ses doigts, tout fin. Il est chaud, papa. Oui. Le soleil l'a chauffé. Tu fais une colline ? Nino tasse le sable. Ça sent la poussière chaude. Bravo. Un enfant arrive trop vite près du bac. Nino sent un choc à l'épaule. Son cœur bat très vite. Stop. Il recule. Il s'éloigne. S'éloigner, c'est marcher vers papa. Nino s'éloigne vers le banc. Papa est le parent au parc. Nino va vers papa. J'ai dit stop. Papa l'écoute. Tu as dit stop. Tu t'es éloigné. Tu es venu vers moi. Bravo, Nino. Nino souffle. Il touche la veste, toute douce. On écoute le nuage mouton ? Il avance tout lentement. Plus tard, Nino va près des balançoires. Il ôte la feuille sèche du siège. Je reste sur le banc. Je suis ton parent au parc. Un enfant arrive trop vite encore. Nino sent un choc, près des chaînes. Nino se souvient. Stop. Il s'éloigne. Il rejoint le parent au parc. Papa est sur le banc. Nino prend sa main. Tu as bien fait. Tu as dit stop. Tu t'es éloigné. Tu es venu vers papa, le parent au parc. Bravo. Les chaînes tintent encore, plus doucement. Le nuage mouton a un peu bougé.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hadrien joue au parc. Le sable est tiède. Un camarade le bouscule près du bac. Hadrien sent son épaule.
-narrateur|Stop. Il recule. Il peut s'éloigner.
-narrateur|Il s'éloigne vers le banc. Papa est le parent au parc. Hadrien va vers papa.
-narrateur|J'ai dit stop. Papa l'écoute.
-narrateur|Hadrien souffle. Plus tard, près des balançoires, un camarade le bouscule encore. Même leçon, autre jeu.
-enfant-m|Stop. Il peut s'éloigner. Il rejoint le parent au parc. Papa est sur le banc.
-narrateur|Hadrien prend sa main.
-papa|Tu as bien fait. On dit stop. On s'éloigne. On va vers papa ou maman, le parent au parc.</t>
+          <t>narrateur|Les chaînes des balançoires font un petit tintement.
+narrateur|Un nuage ressemble à un mouton, tout lent.
+narrateur|Une feuille sèche est posée sur un siège.
+narrateur|Le sable du bac est tiède, presque doux.
+narrateur|Papa étale sa veste sur le banc.
+narrateur|La veste sent le savon et le vent.
+papa|Nino, tu entends les chaînes ?
+enfant-m|Oui.
+enfant-m|Ça tinte, papa.
+papa|Le bac est tiède.
+papa|Les balançoires aussi, plus tard.
+narrateur|En ce moment, Nino creuse au bac.
+narrateur|Le sable coule entre ses doigts, tout fin.
+enfant-m|Il est chaud, papa.
+papa|Oui.
+papa|Le soleil l'a chauffé.
+papa|Tu fais une colline ?
+narrateur|Nino tasse le sable.
+narrateur|Ça sent la poussière chaude.
+papa|Bravo.
+narrateur|Un enfant arrive trop vite près du bac.
+narrateur|Nino sent un choc à l'épaule.
+narrateur|Son cœur bat très vite.
+enfant-m|Stop.
+narrateur|Il recule.
+narrateur|Il s'éloigne.
+narrateur|S'éloigner, c'est marcher vers papa.
+narrateur|Nino s'éloigne vers le banc.
+narrateur|Papa est le parent au parc.
+narrateur|Nino va vers papa.
+enfant-m|J'ai dit stop.
+narrateur|Papa l'écoute.
+papa|Tu as dit stop.
+papa|Tu t'es éloigné.
+papa|Tu es venu vers moi.
+papa|Bravo, Nino.
+narrateur|Nino souffle.
+narrateur|Il touche la veste, toute douce.
+papa|On écoute le nuage mouton ?
+enfant-m|Il avance tout lentement.
+narrateur|Plus tard, Nino va près des balançoires.
+narrateur|Il ôte la feuille sèche du siège.
+papa|Je reste sur le banc.
+papa|Je suis ton parent au parc.
+narrateur|Un enfant arrive trop vite encore.
+narrateur|Nino sent un choc, près des chaînes.
+narrateur|Nino se souvient.
+enfant-m|Stop.
+narrateur|Il s'éloigne.
+narrateur|Il rejoint le parent au parc.
+narrateur|Papa est sur le banc.
+narrateur|Nino prend sa main.
+papa|Tu as bien fait.
+papa|Tu as dit stop.
+papa|Tu t'es éloigné.
+papa|Tu es venu vers papa, le parent au parc.
+papa|Bravo.
+narrateur|Les chaînes tintent encore, plus doucement.
+narrateur|Le nuage mouton a un peu bougé.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1351,7 +1414,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Un camarade bouscule Hadrien. Que fait-il ?</t>
+          <t>Un camarade bouscule Nino. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,10 +1570,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Un camarade bouscule Hadrien. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Un camarade bouscule Nino.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1535,7 +1598,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hadrien a dit stop. Au bac, puis aux balançoires. Il a pu s'éloigner. Il a rejoint le parent au parc.</t>
+          <t>Nino a dit stop. Au bac, puis aux balançoires. Il a pu s'éloigner. Il a rejoint le parent au parc. Tu es venu vers moi, deux fois. Bravo. Tu as fini de souffler ? Oui, papa. C'est du bon travail. Nino pose la feuille sèche sur le banc. Elle est légère, toute croustillante.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1679,7 +1742,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hadrien a dit stop. Au bac, puis aux balançoires. Il a pu s'éloigner. Il a rejoint le parent au parc.</t>
+          <t>narrateur|Nino a dit stop.
+narrateur|Au bac, puis aux balançoires.
+narrateur|Il a pu s'éloigner.
+narrateur|Il a rejoint le parent au parc.
+papa|Tu es venu vers moi, deux fois.
+papa|Bravo.
+papa|Tu as fini de souffler ?
+enfant-m|Oui, papa.
+papa|C'est du bon travail.
+narrateur|Nino pose la feuille sèche sur le banc.
+narrateur|Elle est légère, toute croustillante.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1711,7 +1784,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hadrien reste près du banc. Papa lui tient la main.</t>
+          <t>Nino reste près du banc. Papa lui tient la main. Tu veux un peu d'eau ? Oui. Nino boit une gorgée. On écoute encore les chaînes ? Oui, papa. Le tintement est tout petit, tout loin. Je garde ta main. Le nuage mouton passe au-dessus du parc.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1851,10 +1924,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hadrien reste près du banc. Papa lui tient la main.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nino reste près du banc.
+narrateur|Papa lui tient la main.
+papa|Tu veux un peu d'eau ?
+enfant-m|Oui.
+narrateur|Nino boit une gorgée.
+papa|On écoute encore les chaînes ?
+enfant-m|Oui, papa.
+narrateur|Le tintement est tout petit, tout loin.
+papa|Je garde ta main.
+narrateur|Le nuage mouton passe au-dessus du parc.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1879,7 +1960,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis venu vers toi. Bravo, Nino. Tu as fait du bon travail. Les chaînes tintent encore un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2019,10 +2100,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|J'ai dit stop.
+enfant-m|Je suis venu vers toi.
+papa|Bravo, Nino.
+papa|Tu as fait du bon travail.
+narrateur|Les chaînes tintent encore un peu.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2041,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2079,6 +2164,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.001-07.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-07.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hadrien joue au parc. Le sable est tiède. Un camarade le bouscule près du bac. Hadrien sent son épaule. Il dit : &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Il recule. Il peut s'éloigner. Il s'éloigne vers le banc. Papa est le parent au parc. Hadrien va vers papa. Il dit : j'ai dit stop. Papa l'écoute. Hadrien souffle. Plus tard, près des balançoires, un camarade le bouscule encore. Même leçon, autre jeu. Hadrien dit : stop. Il peut s'éloigner. Il rejoint le parent au parc. Papa est sur le banc. Hadrien prend sa main. Papa dit : tu as bien fait. On dit stop. On s'éloigne. On va vers papa ou maman, le parent au parc.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les chaînes des balançoires font un petit tintement. Un nuage ressemble à un mouton, tout lent. Une feuille sèche est posée sur un siège. Le sable du bac est tiède, presque doux. Papa étale sa veste sur le banc. La veste sent le savon et le vent. Nino, tu entends les chaînes ? Oui. Ça tinte, papa. Le bac est tiède. Les balançoires aussi, plus tard. En ce moment, Nino creuse au bac. Le sable coule entre ses doigts, tout fin. Il est chaud, papa. Oui. Le soleil l'a chauffé. Tu fais une colline ? Nino tasse le sable. Ça sent la poussière chaude. Bravo. Un enfant arrive trop vite près du bac. Nino sent un choc à l'épaule. Son cœur bat très vite. Stop. Il recule. Il s'éloigne. S'éloigner, c'est marcher vers papa. Nino s'éloigne vers le banc. Papa est le parent au parc. Nino va vers papa. J'ai dit stop. Papa l'écoute. Tu as dit stop. Tu t'es éloigné. Tu es venu vers moi. Bravo, Nino. Nino souffle. Il touche la veste, toute douce. On écoute le nuage mouton ? Il avance tout lentement. Plus tard, Nino va près des balançoires. Il ôte la feuille sèche du siège. Je reste sur le banc. Je suis ton parent au parc. Un enfant arrive trop vite encore. Nino sent un choc, près des chaînes. Nino se souvient. Stop. Il s'éloigne. Il rejoint le parent au parc. Papa est sur le banc. Nino prend sa main. Tu as bien fait. Tu as dit stop. Tu t'es éloigné. Tu es venu vers papa, le parent au parc. Bravo. Les chaînes tintent encore, plus doucement. Le nuage mouton a un peu bougé.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Un camarade bouscule Hadrien. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un camarade bouscule Nino. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nino a dit stop. Au bac, puis aux balançoires. Il a pu s'éloigner. Il a rejoint le parent au parc. Tu es venu vers moi, deux fois. Bravo. Tu as fini de souffler ? Oui, papa. C'est du bon travail. Nino pose la feuille sèche sur le banc. Elle est légère, toute croustillante.</t>
+          <t>Nino a dit stop. Au bac, puis aux balançoires. Il a pu s'éloigner. Il a rejoint le parent au parc. Tu es venu vers moi, deux fois. Bravo. Tu as fini de souffler ? Oui, papa. Nino pose la feuille sèche sur le banc. Elle est légère, toute croustillante.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hadrien a dit &lt;emphasis level="moderate"&gt;stop&lt;/emphasis&gt;. Au bac, puis aux balançoires. Il a pu s'éloigner. Il a rejoint le parent au parc.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino a dit stop. Au bac, puis aux balançoires. Il a pu s'éloigner. Il a rejoint le parent au parc. Tu es venu vers moi, deux fois. Bravo. Tu as fini de souffler ? Oui, papa. Nino pose la feuille sèche sur le banc. Elle est légère, toute croustillante.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1750,7 +1750,6 @@
 papa|Bravo.
 papa|Tu as fini de souffler ?
 enfant-m|Oui, papa.
-papa|C'est du bon travail.
 narrateur|Nino pose la feuille sèche sur le banc.
 narrateur|Elle est légère, toute croustillante.</t>
         </is>
@@ -1789,7 +1788,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hadrien reste près du banc. Papa lui tient la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt;.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nino reste près du banc. Papa lui tient la main. Tu veux un peu d'eau ? Oui. Nino boit une gorgée. On écoute encore les chaînes ? Oui, papa. Le tintement est tout petit, tout loin. Je garde ta main. Le nuage mouton passe au-dessus du parc.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1960,12 +1959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit stop. Je suis venu vers toi. Bravo, Nino. Tu as fait du bon travail. Les chaînes tintent encore un peu. L'histoire est finie.</t>
+          <t>J'ai dit stop. Je suis venu vers toi. Bravo, Nino. Les chaînes tintent encore un peu.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit stop. Je suis venu vers toi. Bravo, Nino. Les chaînes tintent encore un peu.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,9 +2102,7 @@
           <t>enfant-m|J'ai dit stop.
 enfant-m|Je suis venu vers toi.
 papa|Bravo, Nino.
-papa|Tu as fait du bon travail.
-narrateur|Les chaînes tintent encore un peu.
-narrateur|L'histoire est finie.</t>
+narrateur|Les chaînes tintent encore un peu.</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2171,6 +2168,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.001-07.xlsx
+++ b/stories/arbres/ATOM-REL.CON.001-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hadrien, papa</t>
+          <t>Nino, papa</t>
         </is>
       </c>
     </row>
